--- a/mlef_pipeline/results/DCR/C23/training_summary.xlsx
+++ b/mlef_pipeline/results/DCR/C23/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,6 +616,736 @@
       </c>
       <c r="W2" t="n">
         <v>251</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RWD_DP</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6862654668166478</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04277304676251148</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6012279000467925</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05246693375598625</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6231520130324847</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.07377409153767539</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5852366625712945</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1293620195605941</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5172735760971057</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.1243266057739229</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3874128919860627</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6646489104116221</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.09094284015988907</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6071632198206603</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.7380952380952381</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.4745762711864407</v>
+      </c>
+      <c r="T3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>604</v>
+      </c>
+      <c r="V3" t="n">
+        <v>97</v>
+      </c>
+      <c r="W3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RWD_DP/rwd-only</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6638357705286838</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.04285614024560847</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5775851346839509</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.03675034963897261</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6863069958221523</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.103912891714021</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4964451170177699</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1187078417711746</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.69234360410831</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.11195563980709</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6149314893072096</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8412698412698413</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3823529411764706</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6805891848264728</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.09073408904302327</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5661407766990292</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2542372881355932</v>
+      </c>
+      <c r="T4" t="n">
+        <v>11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>604</v>
+      </c>
+      <c r="V4" t="n">
+        <v>97</v>
+      </c>
+      <c r="W4" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.64760348583878</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.04219679774502438</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5929077888444555</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05619257345979352</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6314156512334816</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.09954596711068286</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5713470837185894</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1164265102252382</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5396681749622926</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.107631408783937</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5215598050243719</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5538461538461539</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4901960784313725</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4981763570049345</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.09813020240588755</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5132403264016846</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.4936708860759494</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5423728813559322</v>
+      </c>
+      <c r="T5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>642</v>
+      </c>
+      <c r="V5" t="n">
+        <v>116</v>
+      </c>
+      <c r="W5" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6296879863056333</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.04281729362321374</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5677550522750183</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.04283982597708615</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6565410376327371</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1019119297889885</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5013505667384047</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1281029462349115</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6814479638009049</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.09830166559279785</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4482758620689655</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9692307692307692</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.09803921568627451</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6472859901308732</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.09364836328133919</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4465913233685745</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>642</v>
+      </c>
+      <c r="V6" t="n">
+        <v>116</v>
+      </c>
+      <c r="W6" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6643207419414408</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04230709049627512</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6149835628999002</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01820438568008377</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6377771039740524</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.04915905144721697</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.595004230301462</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.07134898728630315</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6268382352941178</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1027562871399084</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.523902651021295</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.09783506154234359</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5105316482696102</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.4230769230769231</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>625</v>
+      </c>
+      <c r="V7" t="n">
+        <v>115</v>
+      </c>
+      <c r="W7" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6350975644787329</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.04313064937548694</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5734069073211655</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05269347517275487</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.625925225336136</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1102120675378928</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5396904562039073</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1300856500013861</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7098651960784315</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.09595419256130033</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6381149742881265</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6303780964797914</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.09569146147959373</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5849224737123507</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3559322033898305</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>625</v>
+      </c>
+      <c r="V8" t="n">
+        <v>115</v>
+      </c>
+      <c r="W8" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.765630261533281</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.05727930114765856</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6849010080969981</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.07323777070201025</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.71665833315217</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.09486564650196061</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6626633227640499</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09806939058150389</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.471774193548387</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.195788088320549</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.425531914893617</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5770588235294116</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1248301530310449</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.578494623655914</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="T9" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>269</v>
+      </c>
+      <c r="V9" t="n">
+        <v>47</v>
+      </c>
+      <c r="W9" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.5942305533729936</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.06802129707521876</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5190337771937571</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.07364480668464286</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.604867014017213</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1467651533636198</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4794673445586413</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1943509183314277</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6653225806451613</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1622378804941408</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4918918918918919</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.7576470588235293</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1093882946866138</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.6011957095129242</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>269</v>
+      </c>
+      <c r="V10" t="n">
+        <v>47</v>
+      </c>
+      <c r="W10" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7089880199867559</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.06289978116310702</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6115823100653586</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.06345791174245417</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6136088907343968</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1236867318196105</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6222497932175352</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.07679504735208177</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4455645161290323</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1879565692184444</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4342592592592592</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.7717647058823529</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1035793803851699</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6932440657334145</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>260</v>
+      </c>
+      <c r="V11" t="n">
+        <v>47</v>
+      </c>
+      <c r="W11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6740111973993136</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.06534110796495041</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.573077675031558</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.02831313151927003</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6415314255395226</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1095387690205638</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5316849816849817</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.119751161467262</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1624847229024757</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5422077922077922</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.7788235294117647</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1044278452272073</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7114264376400299</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>260</v>
+      </c>
+      <c r="V12" t="n">
+        <v>47</v>
+      </c>
+      <c r="W12" t="n">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/mlef_pipeline/results/DCR/C23/training_summary.xlsx
+++ b/mlef_pipeline/results/DCR/C23/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,803 +548,292 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD</t>
+          <t>RWD_DP_FMRAD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6727249988514608</v>
+        <v>0.765630261533281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02696580345621602</v>
+        <v>0.05727930114765856</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6022846297738351</v>
+        <v>0.6849010080969981</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02906556576883322</v>
+        <v>0.07323777070201025</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6808598824340794</v>
+        <v>0.71665833315217</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08488041497135841</v>
+        <v>0.09486564650196061</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5475826280602998</v>
+        <v>0.6626633227640499</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0734958849901296</v>
+        <v>0.09806939058150389</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7143263541192535</v>
+        <v>0.471774193548387</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0623619924142651</v>
+        <v>0.195788088320549</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6395297658767907</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7218934911242604</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5576923076923077</v>
+        <v>0.625</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5542705775940042</v>
+        <v>0.5770588235294116</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07269692280288542</v>
+        <v>0.1248301530310449</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5219047619047619</v>
+        <v>0.578494623655914</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4647887323943662</v>
+        <v>0.58</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5963302752293578</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="T2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U2" t="n">
-        <v>1544</v>
+        <v>269</v>
       </c>
       <c r="V2" t="n">
-        <v>273</v>
+        <v>47</v>
       </c>
       <c r="W2" t="n">
-        <v>251</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_DP</t>
+          <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6862654668166478</v>
+        <v>0.6279885509035809</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04277304676251148</v>
+        <v>0.06659541150773263</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6012279000467925</v>
+        <v>0.5589599307287952</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05246693375598625</v>
+        <v>0.04556437923514402</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6231520130324847</v>
+        <v>0.6448550813906582</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07377409153767539</v>
+        <v>0.129247848714916</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5852366625712945</v>
+        <v>0.4917666648443764</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1293620195605941</v>
+        <v>0.09709268562924159</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5172735760971057</v>
+        <v>0.5786290322580645</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1243266057739229</v>
+        <v>0.1719200093968649</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3874128919860627</v>
+        <v>0.5052631578947369</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.125</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6646489104116221</v>
+        <v>0.6191176470588236</v>
       </c>
       <c r="P3" t="n">
-        <v>0.09094284015988907</v>
+        <v>0.1381766819255706</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6071632198206603</v>
+        <v>0.5997067448680352</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.98</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4745762711864407</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="T3" t="n">
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>604</v>
+        <v>269</v>
       </c>
       <c r="V3" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="W3" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP/rwd-only</t>
+          <t>RWD_DP_PYRAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6638357705286838</v>
+        <v>0.7089880199867559</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04285614024560847</v>
+        <v>0.06289978116310702</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5775851346839509</v>
+        <v>0.6115823100653586</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03675034963897261</v>
+        <v>0.06345791174245417</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6863069958221523</v>
+        <v>0.6136088907343968</v>
       </c>
       <c r="G4" t="n">
-        <v>0.103912891714021</v>
+        <v>0.1236867318196105</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4964451170177699</v>
+        <v>0.6222497932175352</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1187078417711746</v>
+        <v>0.07679504735208177</v>
       </c>
       <c r="J4" t="n">
-        <v>0.69234360410831</v>
+        <v>0.4455645161290323</v>
       </c>
       <c r="K4" t="n">
-        <v>0.11195563980709</v>
+        <v>0.1879565692184444</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6149314893072096</v>
+        <v>0.4342592592592592</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8412698412698413</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3823529411764706</v>
+        <v>0.4375</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6805891848264728</v>
+        <v>0.7717647058823529</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09073408904302327</v>
+        <v>0.1035793803851699</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5661407766990292</v>
+        <v>0.6932440657334145</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.82</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2542372881355932</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>604</v>
+        <v>260</v>
       </c>
       <c r="V4" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="W4" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD_DP_PYRAD/rwd-only</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.64760348583878</v>
+        <v>0.6775329600866894</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04219679774502438</v>
+        <v>0.06480616574336129</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5929077888444555</v>
+        <v>0.6061785327024251</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05619257345979352</v>
+        <v>0.04176571824330157</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6314156512334816</v>
+        <v>0.6937450738395408</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09954596711068286</v>
+        <v>0.06590374667492263</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5713470837185894</v>
+        <v>0.5256188703769348</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1164265102252382</v>
+        <v>0.1018974065229609</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5396681749622926</v>
+        <v>0.6300403225806452</v>
       </c>
       <c r="K5" t="n">
-        <v>0.107631408783937</v>
+        <v>0.1665719928763655</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5215598050243719</v>
+        <v>0.5427547363031233</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5538461538461539</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4901960784313725</v>
+        <v>0.375</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4981763570049345</v>
+        <v>0.7244117647058825</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09813020240588755</v>
+        <v>0.1183584268334841</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5132403264016846</v>
+        <v>0.6932440657334145</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4936708860759494</v>
+        <v>0.82</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5423728813559322</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="T5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U5" t="n">
-        <v>642</v>
+        <v>260</v>
       </c>
       <c r="V5" t="n">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="W5" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RWD_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.6296879863056333</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.04281729362321374</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5677550522750183</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.04283982597708615</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6565410376327371</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.1019119297889885</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.5013505667384047</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1281029462349115</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.6814479638009049</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.09830166559279785</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.4482758620689655</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.9692307692307692</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.09803921568627451</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.6472859901308732</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.09364836328133919</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.4465913233685745</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9873417721518988</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.0847457627118644</v>
-      </c>
-      <c r="T6" t="n">
-        <v>11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>642</v>
-      </c>
-      <c r="V6" t="n">
-        <v>116</v>
-      </c>
-      <c r="W6" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.6643207419414408</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.04230709049627512</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.6149835628999002</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.01820438568008377</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6377771039740524</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.04915905144721697</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.595004230301462</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.07134898728630315</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6268382352941178</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.1027562871399084</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.6166666666666667</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.59375</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.523902651021295</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.09783506154234359</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.5105316482696102</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.4230769230769231</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.6271186440677966</v>
-      </c>
-      <c r="T7" t="n">
-        <v>6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>625</v>
-      </c>
-      <c r="V7" t="n">
-        <v>115</v>
-      </c>
-      <c r="W7" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6350975644787329</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.04313064937548694</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5734069073211655</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.05269347517275487</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.625925225336136</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.1102120675378928</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.5396904562039073</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.1300856500013861</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.7098651960784315</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.09595419256130033</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.6381149742881265</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.6303780964797914</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.09569146147959373</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.5849224737123507</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.3559322033898305</v>
-      </c>
-      <c r="T8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U8" t="n">
-        <v>625</v>
-      </c>
-      <c r="V8" t="n">
-        <v>115</v>
-      </c>
-      <c r="W8" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.765630261533281</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.05727930114765856</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6849010080969981</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.07323777070201025</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.71665833315217</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.09486564650196061</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6626633227640499</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.09806939058150389</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.471774193548387</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.195788088320549</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.425531914893617</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.3225806451612903</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.5770588235294116</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.1248301530310449</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.578494623655914</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="T9" t="n">
-        <v>11</v>
-      </c>
-      <c r="U9" t="n">
-        <v>269</v>
-      </c>
-      <c r="V9" t="n">
-        <v>47</v>
-      </c>
-      <c r="W9" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.5942305533729936</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.06802129707521876</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.5190337771937571</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.07364480668464286</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.604867014017213</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.1467651533636198</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.4794673445586413</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.1943509183314277</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.6653225806451613</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.1622378804941408</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.4918918918918919</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.9354838709677419</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.7576470588235293</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.1093882946866138</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.6011957095129242</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="T10" t="n">
-        <v>11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>269</v>
-      </c>
-      <c r="V10" t="n">
-        <v>47</v>
-      </c>
-      <c r="W10" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.7089880199867559</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.06289978116310702</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6115823100653586</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.06345791174245417</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.6136088907343968</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.1236867318196105</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6222497932175352</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.07679504735208177</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.4455645161290323</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.1879565692184444</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.4342592592592592</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.4516129032258064</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.7717647058823529</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.1035793803851699</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.6932440657334145</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.5588235294117647</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>260</v>
-      </c>
-      <c r="V11" t="n">
-        <v>47</v>
-      </c>
-      <c r="W11" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.6740111973993136</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.06534110796495041</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.573077675031558</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.02831313151927003</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.6415314255395226</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.1095387690205638</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5316849816849817</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.119751161467262</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.1624847229024757</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.5422077922077922</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.7741935483870968</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.7788235294117647</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.1044278452272073</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.7114264376400299</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="T12" t="n">
-        <v>8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>260</v>
-      </c>
-      <c r="V12" t="n">
-        <v>47</v>
-      </c>
-      <c r="W12" t="n">
         <v>84</v>
       </c>
     </row>

--- a/mlef_pipeline/results/DCR/C23/training_summary.xlsx
+++ b/mlef_pipeline/results/DCR/C23/training_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,292 +548,803 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD_DP_FMRAD</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.765630261533281</v>
+        <v>0.6727249988514608</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05727930114765856</v>
+        <v>0.02696580345621602</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6849010080969981</v>
+        <v>0.6022846297738351</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07323777070201025</v>
+        <v>0.02906556576883322</v>
       </c>
       <c r="F2" t="n">
-        <v>0.71665833315217</v>
+        <v>0.6808598824340794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09486564650196061</v>
+        <v>0.08488041497135841</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6626633227640499</v>
+        <v>0.5475826280602998</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09806939058150389</v>
+        <v>0.0734958849901296</v>
       </c>
       <c r="J2" t="n">
-        <v>0.471774193548387</v>
+        <v>0.7143263541192535</v>
       </c>
       <c r="K2" t="n">
-        <v>0.195788088320549</v>
+        <v>0.0623619924142651</v>
       </c>
       <c r="L2" t="n">
-        <v>0.425531914893617</v>
+        <v>0.6395297658767907</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.7218934911242604</v>
       </c>
       <c r="N2" t="n">
-        <v>0.625</v>
+        <v>0.5576923076923077</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5770588235294116</v>
+        <v>0.5542705775940042</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1248301530310449</v>
+        <v>0.07269692280288542</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.578494623655914</v>
+        <v>0.5219047619047619</v>
       </c>
       <c r="R2" t="n">
-        <v>0.58</v>
+        <v>0.4647887323943662</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5963302752293578</v>
       </c>
       <c r="T2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>269</v>
+        <v>1544</v>
       </c>
       <c r="V2" t="n">
-        <v>47</v>
+        <v>273</v>
       </c>
       <c r="W2" t="n">
-        <v>84</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_DP_FMRAD/rwd-only</t>
+          <t>RWD_DP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6279885509035809</v>
+        <v>0.6862654668166478</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06659541150773263</v>
+        <v>0.04277304676251148</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5589599307287952</v>
+        <v>0.6012279000467925</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04556437923514402</v>
+        <v>0.05246693375598625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6448550813906582</v>
+        <v>0.6231520130324847</v>
       </c>
       <c r="G3" t="n">
-        <v>0.129247848714916</v>
+        <v>0.07377409153767539</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4917666648443764</v>
+        <v>0.5852366625712945</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09709268562924159</v>
+        <v>0.1293620195605941</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5786290322580645</v>
+        <v>0.5172735760971057</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1719200093968649</v>
+        <v>0.1243266057739229</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5052631578947369</v>
+        <v>0.3874128919860627</v>
       </c>
       <c r="M3" t="n">
-        <v>0.967741935483871</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="N3" t="n">
-        <v>0.125</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6191176470588236</v>
+        <v>0.6646489104116221</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1381766819255706</v>
+        <v>0.09094284015988907</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5997067448680352</v>
+        <v>0.6071632198206603</v>
       </c>
       <c r="R3" t="n">
-        <v>0.98</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.4745762711864407</v>
       </c>
       <c r="T3" t="n">
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>269</v>
+        <v>604</v>
       </c>
       <c r="V3" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="W3" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP_PYRAD</t>
+          <t>RWD_DP/rwd-only</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7089880199867559</v>
+        <v>0.6638357705286838</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06289978116310702</v>
+        <v>0.04285614024560847</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6115823100653586</v>
+        <v>0.5775851346839509</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06345791174245417</v>
+        <v>0.03675034963897261</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6136088907343968</v>
+        <v>0.6863069958221523</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1236867318196105</v>
+        <v>0.103912891714021</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6222497932175352</v>
+        <v>0.4964451170177699</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07679504735208177</v>
+        <v>0.1187078417711746</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4455645161290323</v>
+        <v>0.69234360410831</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1879565692184444</v>
+        <v>0.11195563980709</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4342592592592592</v>
+        <v>0.6149314893072096</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.8412698412698413</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4375</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7717647058823529</v>
+        <v>0.6805891848264728</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1035793803851699</v>
+        <v>0.09073408904302327</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6932440657334145</v>
+        <v>0.5661407766990292</v>
       </c>
       <c r="R4" t="n">
-        <v>0.82</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.2542372881355932</v>
       </c>
       <c r="T4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>260</v>
+        <v>604</v>
       </c>
       <c r="V4" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="W4" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>RWD_FMRAD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6471463585434174</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.04227732186611932</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5986251137317025</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05812787101842695</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6774159520295377</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1409031149634596</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5421611277785254</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09649171581974864</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5951734539969834</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.105496376050671</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5842293906810037</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5846153846153846</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5177000643638705</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0992178197394035</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.4926470588235294</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.4177215189873418</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5932203389830508</v>
+      </c>
+      <c r="T5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>642</v>
+      </c>
+      <c r="V5" t="n">
+        <v>116</v>
+      </c>
+      <c r="W5" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6296879863056333</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.04281729362321374</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5677550522750183</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.04283982597708615</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6565410376327371</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1019119297889885</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5013505667384047</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1281029462349115</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6814479638009049</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.09830166559279785</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4482758620689655</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9692307692307692</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.09803921568627451</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6472859901308732</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.09364836328133919</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4465913233685745</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>642</v>
+      </c>
+      <c r="V6" t="n">
+        <v>116</v>
+      </c>
+      <c r="W6" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6643207419414408</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04230709049627512</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6149835628999002</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01820438568008377</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6377771039740524</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.04915905144721697</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.595004230301462</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.07134898728630315</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6268382352941178</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1027562871399084</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.523902651021295</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.09783506154234359</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5105316482696102</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.4230769230769231</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>625</v>
+      </c>
+      <c r="V7" t="n">
+        <v>115</v>
+      </c>
+      <c r="W7" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6350975644787329</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.04313064937548694</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5734069073211655</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05269347517275487</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.625925225336136</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1102120675378928</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5396904562039073</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1300856500013861</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7098651960784315</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.09595419256130033</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6381149742881265</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6303780964797914</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.09569146147959373</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5849224737123507</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3559322033898305</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>625</v>
+      </c>
+      <c r="V8" t="n">
+        <v>115</v>
+      </c>
+      <c r="W8" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.765630261533281</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.05727930114765856</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6849010080969981</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.07323777070201025</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.71665833315217</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.09486564650196061</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6626633227640499</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09806939058150389</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.471774193548387</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.195788088320549</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.425531914893617</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5770588235294116</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1248301530310449</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.578494623655914</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="T9" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>269</v>
+      </c>
+      <c r="V9" t="n">
+        <v>47</v>
+      </c>
+      <c r="W9" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6279885509035809</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.06659541150773263</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5589599307287952</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04556437923514402</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6448550813906582</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.129247848714916</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4917666648443764</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.09709268562924159</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5786290322580645</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1719200093968649</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5052631578947369</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.6191176470588236</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1381766819255706</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5997067448680352</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2647058823529412</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>269</v>
+      </c>
+      <c r="V10" t="n">
+        <v>47</v>
+      </c>
+      <c r="W10" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7089880199867559</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.06289978116310702</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6115823100653586</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.06345791174245417</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6136088907343968</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1236867318196105</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6222497932175352</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.07679504735208177</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4455645161290323</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1879565692184444</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4342592592592592</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.7717647058823529</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1035793803851699</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6932440657334145</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>260</v>
+      </c>
+      <c r="V11" t="n">
+        <v>47</v>
+      </c>
+      <c r="W11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>RWD_DP_PYRAD/rwd-only</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B12" t="n">
         <v>0.6775329600866894</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C12" t="n">
         <v>0.06480616574336129</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D12" t="n">
         <v>0.6061785327024251</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E12" t="n">
         <v>0.04176571824330157</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F12" t="n">
         <v>0.6937450738395408</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G12" t="n">
         <v>0.06590374667492263</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H12" t="n">
         <v>0.5256188703769348</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I12" t="n">
         <v>0.1018974065229609</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J12" t="n">
         <v>0.6300403225806452</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.1665719928763655</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K12" t="n">
+        <v>0.1665719928763656</v>
+      </c>
+      <c r="L12" t="n">
         <v>0.5427547363031233</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M12" t="n">
         <v>0.7096774193548387</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N12" t="n">
         <v>0.375</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O12" t="n">
         <v>0.7244117647058825</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P12" t="n">
         <v>0.1183584268334841</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q12" t="n">
         <v>0.6932440657334145</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R12" t="n">
         <v>0.82</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S12" t="n">
         <v>0.5588235294117647</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T12" t="n">
         <v>8</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U12" t="n">
         <v>260</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V12" t="n">
         <v>47</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W12" t="n">
         <v>84</v>
       </c>
     </row>
